--- a/docs/Mapping_casi_uso/unioni_civili/Sciogl_UnCiv_008.xlsx
+++ b/docs/Mapping_casi_uso/unioni_civili/Sciogl_UnCiv_008.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="175">
   <si>
     <t>Sezione</t>
   </si>
@@ -59,7 +59,7 @@
     <t>NO</t>
   </si>
   <si>
-    <t>193.25</t>
+    <t>193-terdecies</t>
   </si>
   <si>
     <t>Si puo' ignorare la sezione per</t>
@@ -380,7 +380,7 @@
     <t>siglaProvinciaEnte</t>
   </si>
   <si>
-    <t>192.13,193.25</t>
+    <t>193-terdecies,192.13</t>
   </si>
   <si>
     <t>Comune ente</t>
@@ -513,6 +513,9 @@
   </si>
   <si>
     <t>evento.trascrizioneUnioneCivile.atto.enteEstero</t>
+  </si>
+  <si>
+    <t>evento.trascrizioneUnioneCivile.ricevutaDaPrivatoCittadino,=,true</t>
   </si>
   <si>
     <t>Anagrafica Consolato</t>
@@ -3683,7 +3686,7 @@
         <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135">
@@ -3706,7 +3709,7 @@
         <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="136">
@@ -3729,7 +3732,7 @@
         <v>10</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137">
@@ -3752,7 +3755,7 @@
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="138">
@@ -3772,10 +3775,10 @@
         <v>121</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="139">
@@ -3798,7 +3801,7 @@
         <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="140">
@@ -3818,10 +3821,10 @@
         <v>126</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="141">
@@ -3829,7 +3832,7 @@
         <v>165</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>14</v>
@@ -3838,13 +3841,13 @@
         <v>166</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="142">
@@ -3852,7 +3855,7 @@
         <v>165</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>14</v>
@@ -3861,13 +3864,13 @@
         <v>166</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="143">
@@ -3890,7 +3893,7 @@
         <v>10</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="144">
@@ -3913,15 +3916,15 @@
         <v>10</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>9</v>
@@ -3930,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
